--- a/dd_list.xlsx
+++ b/dd_list.xlsx
@@ -2554,7 +2554,7 @@
     <t>티셔츠</t>
   </si>
   <si>
-    <t>촉각언어 그래픽 티셔츠 3종</t>
+    <t>촉각언어 그래픽 티셔츠</t>
   </si>
   <si>
     <t>등에서 무슨 일이 일어나고 있는 것 같은 티셔츠</t>
